--- a/04 - MID/03 - Delete/01 - Demand/Data.xlsx
+++ b/04 - MID/03 - Delete/01 - Demand/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - MID\03 - Delete\01 - Demand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551DD812-C212-4683-AC8F-94566A389DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF2486C-F7C3-4CFB-8791-8B4ED13C46C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{841C4129-0CB3-4066-B34E-E8845E3509BE}"/>
   </bookViews>
@@ -439,44 +439,44 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>685601397939</v>
+        <v>685601401883</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>685601397938</v>
+        <v>685601401884</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>685601397937</v>
+        <v>685601401885</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>685601397936</v>
+        <v>685601401887</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>685601397935</v>
+        <v>685601401890</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>685601397934</v>
+        <v>685601401892</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>685601397933</v>
+        <v>685601401894</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>685601397932</v>
+        <v>685601401895</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -485,7 +485,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>685601397931</v>
+        <v>685601401896</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -494,7 +494,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>685601397930</v>
+        <v>685601401897</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -503,7 +503,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>685601397929</v>
+        <v>685601401898</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -511,61 +511,79 @@
       <c r="M12" s="3"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2">
+        <v>685601401899</v>
+      </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2">
+        <v>685601401900</v>
+      </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2">
+        <v>685601401902</v>
+      </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
+      <c r="A16" s="2">
+        <v>685601401903</v>
+      </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2">
+        <v>685601401904</v>
+      </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2">
+        <v>685601401905</v>
+      </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2">
+        <v>685601401906</v>
+      </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2">
+        <v>685601401907</v>
+      </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
+      <c r="A21" s="2">
+        <v>685601401908</v>
+      </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>

--- a/04 - MID/03 - Delete/01 - Demand/Data.xlsx
+++ b/04 - MID/03 - Delete/01 - Demand/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - MID\03 - Delete\01 - Demand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF2486C-F7C3-4CFB-8791-8B4ED13C46C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C804234A-1015-4922-8513-910C46E91FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{841C4129-0CB3-4066-B34E-E8845E3509BE}"/>
   </bookViews>
@@ -439,44 +439,44 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>685601401883</v>
+        <v>685601403955</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>685601401884</v>
+        <v>685601403956</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>685601401885</v>
+        <v>685601403959</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>685601401887</v>
+        <v>685601403960</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>685601401890</v>
+        <v>685601403962</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>685601401892</v>
+        <v>685601403963</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>685601401894</v>
+        <v>685601403964</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>685601401895</v>
+        <v>685601403965</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -485,7 +485,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>685601401896</v>
+        <v>685601403966</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -494,7 +494,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>685601401897</v>
+        <v>685601403966</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -503,7 +503,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>685601401898</v>
+        <v>685601403967</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -512,7 +512,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>685601401899</v>
+        <v>685601403969</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -521,7 +521,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>685601401900</v>
+        <v>685601403973</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
@@ -529,61 +529,47 @@
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>685601401902</v>
-      </c>
+      <c r="A15" s="2"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>685601401903</v>
-      </c>
+      <c r="A16" s="2"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>685601401904</v>
-      </c>
+      <c r="A17" s="2"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>685601401905</v>
-      </c>
+      <c r="A18" s="2"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>685601401906</v>
-      </c>
+      <c r="A19" s="2"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>685601401907</v>
-      </c>
+      <c r="A20" s="2"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>685601401908</v>
-      </c>
+      <c r="A21" s="2"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>

--- a/04 - MID/03 - Delete/01 - Demand/Data.xlsx
+++ b/04 - MID/03 - Delete/01 - Demand/Data.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - MID\03 - Delete\01 - Demand\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mao8ct\Desktop\PyAutomateSAP\04 - MID\03 - Delete\01 - Demand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C804234A-1015-4922-8513-910C46E91FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E81B04-6481-4DEC-A7D1-329A89D033C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{841C4129-0CB3-4066-B34E-E8845E3509BE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{841C4129-0CB3-4066-B34E-E8845E3509BE}"/>
   </bookViews>
   <sheets>
     <sheet name="LocInst" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LocInst!$A$1:$A$2</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -426,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D997F1F-30FE-4A2A-B694-A9178A4FC344}">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -439,44 +442,56 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>685601403955</v>
+        <v>685601397299</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>685601403956</v>
+        <v>685601397301</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>685601403959</v>
+        <v>685601402487</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>685601403960</v>
-      </c>
+        <v>685601406960</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>685601403962</v>
-      </c>
+        <v>685601410319</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>685601403963</v>
-      </c>
+        <v>685601410318</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>685601403964</v>
-      </c>
+        <v>685601410314</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>685601403965</v>
+        <v>685601410312</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -485,7 +500,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>685601403966</v>
+        <v>685601409761</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -494,7 +509,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>685601403966</v>
+        <v>685601409760</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -503,7 +518,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>685601403967</v>
+        <v>685601409574</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -512,7 +527,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>685601403969</v>
+        <v>685601409573</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -521,78 +536,172 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>685601403973</v>
-      </c>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+        <v>685601409571</v>
+      </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="A15" s="2">
+        <v>685601409109</v>
+      </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
+      <c r="A16" s="2">
+        <v>685601409108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>685601409107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>685601408944</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>685601408091</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>685601407528</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>685601413739</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>685601413111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>685601413110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>685601413109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>685601413108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>685601413107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>685601413105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>685601413103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>685601413067</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>685601412900</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>685601412899</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>685601412777</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>685601411200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>685601410322</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>685601410320</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>685601418247</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>685601418125</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>685601417923</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>685601417922</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>685601416976</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>685601416975</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>685601416706</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>685601416704</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>685601416703</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>685601414925</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>685601414761</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
